--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -590,10 +590,14 @@
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Next.js 16 (Turbopack) + TS + ESLint scaffolded, plus Prettier, Husky pre-commit (lint-staged), .env.example, README with git-workflow notes. lint/build verified locally.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="9">
       <c r="A4" s="11" t="n">
@@ -7957,10 +7961,12 @@
       <c r="C3" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="11" t="n"/>
+      <c r="D3" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F3" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -638,10 +638,14 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Vitest for unit/API tests (sample: src/modules/kernel/health.ts + its route), Playwright for E2E (e2e/health.spec.ts). Playwright configured with channel: chrome (system Chrome) because this sandbox cannot download the bundled Chromium binary over the network (CDN request timeout) - verified passing locally against system Chrome; CI will need Chrome available on the runner (ubuntu-latest/windows-latest images ship it) or a switch to bundled chromium download.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="9">
       <c r="A5" s="11" t="n">
@@ -7985,10 +7989,12 @@
       <c r="C4" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="11" t="n"/>
+      <c r="D4" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F4" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -686,10 +686,14 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Prisma 7 + PostgreSQL wired up via the pg driver adapter (schema.prisma has no url field in Prisma 7 - connection lives in prisma7.config.ts + the adapter). Local dev DB is npx prisma dev (embedded PGlite Postgres, no Docker needed - Docker Desktop would not start in this sandbox). Note: PGlite does not support native extensions (pgcrypto attempt failed) - stick to Prisma-side ID generation (uuid()/cuid()), not DB extensions, for portability. Kernel db client (src/modules/kernel/db.ts) added with a passing automated test that runs a real query against the live dev DB. No domain models yet - that is Day 5.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55.2" customHeight="1" s="9">
       <c r="A6" s="11" t="n">
@@ -8013,10 +8017,12 @@
       <c r="C5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="11" t="n"/>
+      <c r="D5" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F5" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -734,10 +734,14 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>Organisation, Department, Role, User models in prisma/schema.prisma (migration 20260918094921_core_schema). Organisation is the tenant root (no org_id on itself); Department/Role/User all carry organisationId with cascade delete, plus a unique(organisationId, name/email) constraint. IDs are Prisma-generated UUIDs (not a DB extension - see Day 4 note). department/roleId on User are nullable at the DB level; Day 20 (Create employee) will decide whether to require them at the validation layer. 5 automated tests in src/modules/identity/schema.test.ts cover create/read, relations, duplicate-name rejection, and cascade delete.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="9">
       <c r="A7" s="11" t="n">
@@ -8041,10 +8045,12 @@
       <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="11" t="n"/>
+      <c r="D6" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F6" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -782,10 +782,14 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Shared ApiError class + toApiErrorResponse() (src/modules/kernel/errors.ts) map ApiError/ZodError/unknown errors to one predictable {error:{code,message,details?}} JSON shape. zod is the standard validation library. Reference implementation wired into a new POST /api/health/echo route (validate-then-respond pattern every future route copies). 6 automated tests cover valid payload, validation failure, and malformed JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="9">
       <c r="A8" s="11" t="n">
@@ -8069,10 +8073,12 @@
       <c r="C7" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="11" t="n"/>
+      <c r="D7" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F7" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -830,10 +830,14 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>AppShell component (src/components/AppShell.tsx): sticky header + off-canvas sidebar nav, CSS-media-query responsive (sidebar always visible &gt;=768px, toggled via a menu button below that). Replaced the default create-next-app starter homepage. Also fixed a real flakiness bug found while testing this: Vitest running test files in parallel was destabilizing the PGlite dev DB connection (fileParallelism disabled + pool max + explicit  in db-touching tests - see dev_environment memory). Playwright desktop+mobile viewport smoke test in e2e/app-shell.spec.ts, both passing.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="9">
       <c r="A9" s="11" t="n">
@@ -8097,10 +8101,12 @@
       <c r="C8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="11" t="n"/>
+      <c r="D8" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F8" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -878,10 +878,14 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Structured JSON logging via pino (src/modules/kernel/logging.ts, pino-pretty in dev only). Wired into the shared error handler from Day 6: toApiErrorResponse() logs unexpected errors at error level (with the full error object) and handled ApiErrors at warn level (code + status, no stack noise) - so every route that already follows the Day 6 convention gets logging for free with no extra code. 2 automated tests: one verifies pino emits a structured JSON line with level/time/msg/fields, one verifies the error handler actually calls the logger on an unexpected error.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="9">
       <c r="A10" s="11" t="n">
@@ -8125,10 +8129,12 @@
       <c r="C9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="11" t="n"/>
+      <c r="D9" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F9" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -926,10 +926,14 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Idempotent seed (prisma/seed-data.ts: seedDatabase(), all upserts) seeding one organisation, 3 departments, 3 roles, 1 owner user. Wired via prisma7.config.ts migrations.seed using tsx (plain node --experimental-strip-types could not resolve the @/* tsconfig path alias). npm run db:seed -&gt; prisma db seed. Verified idempotent by running twice locally with no errors/duplicates. 2 automated tests (prisma/seed-data.test.ts) cover the happy path and re-running without duplication.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28.35" customHeight="1" s="9">
       <c r="A11" s="11" t="n">
@@ -8153,10 +8157,12 @@
       <c r="C10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="11" t="n"/>
+      <c r="D10" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F10" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -974,10 +974,14 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="n"/>
+          <t>Done (pending first push to verify green)</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>.github/workflows/ci.yml: on push/PR to any branch, a Postgres 16 service container, npm ci, prisma migrate deploy, lint, typecheck, format:check, vitest, build, then Playwright e2e (ubuntu-latest ships Chrome, matching the channel:"chrome" config from Day 3). YAML validated locally. The literal acceptance check (a deliberately-broken test fails the pipeline, a passing one goes green) needs an actual push to github.com/SakshiK2503/ai-firm-management to observe - the repo has a configured origin remote but nothing has been pushed yet this session; flagged to the founder rather than pushed without asking.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="9">
       <c r="A12" s="11" t="n">
@@ -8181,10 +8185,12 @@
       <c r="C11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="11" t="n"/>
+      <c r="D11" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done (pending push)</t>
         </is>
       </c>
       <c r="F11" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1022,10 +1022,14 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Password login: User.passwordHash + a DB-backed Session model (org_id-scoped, revocable - not a stateless JWT, per human-override-always-wins). Kernel owns session/password primitives (bcryptjs hashing, NextRequest/NextResponse-based cookie helpers - deliberately not next/headers cookies() so it stays unit-testable outside a real request). Identity owns the login() service. POST /api/auth/login + GET /api/auth/me + a real /login page (UI, not just API - Definition of Done asks for both where applicable). Known simplification: login looks up by email globally, not org-scoped, since only one org exists (flagged, not a real multi-tenant flow). 9 automated tests (password hashing, login service, both routes) + 2 new Playwright E2E cases (valid login redirects, invalid login shows an error). CI updated to seed the DB before running e2e.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="9">
       <c r="A13" s="11" t="n">
@@ -8209,10 +8213,12 @@
       <c r="C12" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="11" t="n"/>
+      <c r="D12" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1070,10 +1070,14 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Sliding session expiry: getCurrentUser() + refreshSession() extend a valid session another full 7 days on each /api/auth/me check, and the cookie is re-attached with the new expiry - so an active session does not expire mid-use. POST /api/auth/logout deletes the session row and clears the cookie (idempotent - logging out twice does not error). AppShell now shows a Log out button when signed in; fixed a real bug found while testing it - AppShell lives in the root layout so it never remounts on client-side nav from /login to /, so its one-time auth check never re-ran after signing in (fixed by re-running the check on every pathname change). 8 new automated tests (session lifecycle, refresh-on-check, logout) + 2 new Playwright E2E cases (refresh keeps you logged in, logout actually invalidates the session server-side).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="9">
       <c r="A14" s="11" t="n">
@@ -8237,10 +8241,12 @@
       <c r="C13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="11" t="n"/>
+      <c r="D13" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F13" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1118,10 +1118,14 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Protection lives in Server Components, not middleware: Prisma pg driver needs the Node.js runtime, not Edge, which is what middleware runs in by default. A (protected) route group + layout (src/app/(protected)/layout.tsx) calls requireUser() (redirect to /login if no valid session) and renders AppShell; /login is a sibling outside the group and redirects to / if already logged in. AppShell simplified to take userName as a prop from the server layout instead of self-polling /api/auth/me (removes the Day 12 pathname-effect workaround entirely). 2 new Playwright E2E cases for the actual acceptance check (logged-out direct URL blocked; logged-in visiting /login bounces to /). Spent a long stretch chasing what looked like a route-protection bug that was actually prisma dev (PGlite) crashing/losing data under sustained session load - confirmed via curl + the browser tool that the auth/redirect logic itself was correct throughout. Also dropped Playwright to workers:1 (same fix as Vitest fileParallelism:false) - real logins/navigations from parallel workers were their own separate source of flakiness against PGlite.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="9">
       <c r="A15" s="11" t="n">
@@ -8265,10 +8269,12 @@
       <c r="C14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="11" t="n"/>
+      <c r="D14" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F14" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1166,10 +1166,14 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="n"/>
+          <t>Done - pending founder review</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>docs/RBAC.md: role-permission matrix for the 3 seeded roles (Partner/Manager/Preparer), fixed hierarchy (Partner is a superset of Manager is a superset of Preparer), NOT a custom-role builder - flagged for the founder to confirm since the acceptance check for this row is literally a human review, and the specific grants are a proposal. Code representation in src/modules/kernel/rbac/permissions.ts (Permission/SystemRole types, ROLE_PERMISSIONS, hasPermission()). Known gap flagged in the doc: department-level scoping (a Manager should probably only see their own department, not firm-wide) is not enforceable yet since Task does not exist as a table. 7 automated tests validate matrix structure/hierarchy, not enforcement (thats Day 15). No enforcement wiring yet - by design, that is Day 15.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="9">
       <c r="A16" s="11" t="n">
@@ -8293,10 +8297,12 @@
       <c r="C15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="11" t="n"/>
+      <c r="D15" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done - pending founder review</t>
         </is>
       </c>
       <c r="F15" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Done - pending founder review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>docs/RBAC.md: role-permission matrix for the 3 seeded roles (Partner/Manager/Preparer), fixed hierarchy (Partner is a superset of Manager is a superset of Preparer), NOT a custom-role builder - flagged for the founder to confirm since the acceptance check for this row is literally a human review, and the specific grants are a proposal. Code representation in src/modules/kernel/rbac/permissions.ts (Permission/SystemRole types, ROLE_PERMISSIONS, hasPermission()). Known gap flagged in the doc: department-level scoping (a Manager should probably only see their own department, not firm-wide) is not enforceable yet since Task does not exist as a table. 7 automated tests validate matrix structure/hierarchy, not enforcement (thats Day 15). No enforcement wiring yet - by design, that is Day 15.</t>
+          <t>Reviewed by founder and revised (docs/RBAC.md Founder review section has the full diff/reasoning): (1) roles are now data - a Permission catalog (code) + RolePermission join table (DB, seeded by prisma/rbac-seed-data.ts) - enforcement will query roleHasPermission() and never branch on a role name, so adding a role later is a data change not a code change; (2) named the collapse of a fuller 5-tier PRD hierarchy into 3 roles as a conscious simplification (Partner absorbs Super Admin + Department Head); (3) client visibility scoped to assigned-only for Preparer (flagged as a known gap pending Client/Task tables); (4) task:delete replaced with task:cancel (soft/auditable, no material action disappears); (5) client:manage split into editContact (Manager+) vs editStructural (Partner-only); (6) auditLog:view made explicitly the only audit permission that will ever exist for anyone. 15 automated tests total (was 7) covering catalog integrity, grant hierarchy, and DB-integration (seeded grants actually resolve correctly via roleHasPermission).</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Done - pending founder review</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F15" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -974,7 +974,7 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>Done (pending first push to verify green)</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
@@ -1214,10 +1214,14 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>requirePermission(request, permission) (src/modules/kernel/rbac/enforce.ts): the one enforcement primitive every protected route calls - 401 if no session, 403 if the role lacks the permission (never checks a role name). GET /api/organisation is the reference implementation (Partner-only, since organisation:manage is Partner-only per Day 14). Seed data now has 3 sample users (owner=Partner, manager=Manager, preparer=Preparer, same dev password) specifically so allowed/denied behavior is actually testable, not just theoretical. 8 new unit/API tests + 1 new Playwright E2E test (login as Partner -&gt; 200, login as Manager -&gt; 403) prove real allow/deny behavior end-to-end, not just the permission matrix in isolation.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="9">
       <c r="A17" s="11" t="n">
@@ -1258,10 +1262,14 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>server-only guard on session.ts (the one module thats genuinely Next-app-exclusive - db.ts and password.ts stay unguarded on purpose since prisma/seed-data.ts legitimately imports them outside the app; db.ts already has strong inherent protection since @prisma/client+pg depend on Node net/tls that cannot bundle into a browser build anyway). Security headers (X-Content-Type-Options, X-Frame-Options, Referrer-Policy, Permissions-Policy, HSTS) via next.config.ts headers() - verified live via curl and a new Playwright test. A real Content-Security-Policy is explicitly deferred to the Audit &amp; Security hardening phase (Day 131+), not attempted here - a wrong CSP silently breaks fonts/hydration and deserves its own day, not a guess bolted onto a 1-hour baseline day. New npm run verify:no-secrets script scans the actual built client bundle (.next/static) for the real DATABASE_URL value - wired into CI right after the build step. Also found and fixed a real bug while building this: the server-only npm package breaks under both Vitest (fixed via a resolve.alias to a no-op shim) and tsx-run scripts (fixed by not guarding files scripts legitimately need) - see dev-environment memory.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="9">
       <c r="A18" s="11" t="n">
@@ -8206,7 +8214,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Done (pending push)</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F11" s="11" t="n"/>
@@ -8321,10 +8329,12 @@
       <c r="C16" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="11" t="n"/>
+      <c r="D16" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F16" s="11" t="n"/>
@@ -8343,10 +8353,12 @@
       <c r="C17" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="11" t="n"/>
+      <c r="D17" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F17" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -439,7 +439,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:J168"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" style="8" min="1" max="2"/>
     <col width="28" customWidth="1" style="8" min="3" max="4"/>
@@ -1310,10 +1310,14 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>POST /api/departments + department.service.ts createDepartment(). Duplicate prevention comes free from the Day 5 @@unique([organisationId, name]) constraint - the service just maps the P2002 into a clean 409 CONFLICT (new shared src/modules/kernel/db-errors.ts helper, reusable for every future unique-constrained resource). department:manage is Partner-only per Day 14s matrix.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="9">
       <c r="A19" s="11" t="n">
@@ -1354,10 +1358,14 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>GET /api/departments (?search=, ?includeInactive=) + listDepartments(). Built the whole Departments admin page (create+list+search+edit/disable) as one screen rather than a create-only page on Day 17 alone, since that is how a real admin UI would actually be laid out - founder pre-authorized batching multiple days when it does not add risk.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="9">
       <c r="A20" s="11" t="n">
@@ -1398,10 +1406,14 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>PATCH /api/departments/[id] (rename and/or isActive toggle) + updateDepartment(), 404s if the department does not exist or belongs to a different org (org-scoping enforced, not just filtered). Disable/enable both verified via API tests, service tests, and E2E. Note on the acceptance check wording ("disabled dept cannot receive new work"): nothing currently assigns work to a department (no Task table, Employee creation is Day 20, not yet built at this point) - deferred the actual guard to Day 20s employee-creation validation, which is next.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="9">
       <c r="A21" s="11" t="n">
@@ -7937,7 +7949,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:F103"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" style="8" min="1" max="1"/>
     <col width="34" customWidth="1" style="8" min="2" max="2"/>
@@ -8377,10 +8389,12 @@
       <c r="C18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="11" t="n"/>
+      <c r="D18" s="11" t="n">
+        <v>3</v>
+      </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
@@ -10270,7 +10284,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" style="8" min="1" max="1"/>
     <col width="12" customWidth="1" style="8" min="2" max="2"/>
@@ -11352,7 +11366,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" style="8" min="1" max="1"/>
     <col width="15" customWidth="1" style="8" min="2" max="2"/>
@@ -11558,7 +11572,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" style="8" min="1" max="1"/>
     <col width="110" customWidth="1" style="8" min="2" max="2"/>
@@ -11682,7 +11696,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" style="8" min="1" max="1"/>
     <col width="20" customWidth="1" style="8" min="2" max="2"/>
@@ -11769,7 +11783,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:D39"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" style="8" min="1" max="2"/>
     <col width="14" customWidth="1" style="8" min="3" max="3"/>
@@ -12649,7 +12663,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
     <col width="58" customWidth="1" style="8" min="2" max="2"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1454,10 +1454,14 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>POST /api/employees + employee.service.ts createEmployee(). department/role assignment required (not nullable at the validation layer, even though the DB column allows null - Day 5s deferred decision). Closes the Day 19 gap: creating an employee in a disabled department is rejected (400 DEPARTMENT_DISABLED). employee:manage is Partner-only; employee:view (list/detail) is Manager+Partner per Day 14s matrix. Responses use Prisma select (not include) so passwordHash is never even fetched, not just stripped after the fact.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="9">
       <c r="A22" s="11" t="n">
@@ -1498,10 +1502,14 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>GET /api/employees (?search= by name/email, ?includeInactive=) + listEmployees(). Employees admin page shows the list to Manager+Partner but only shows the create form to Partner (employee:manage) - built as one screen with Day 20/22/23 rather than 4 separate pages, same reasoning as Departments.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="9">
       <c r="A23" s="11" t="n">
@@ -1542,10 +1550,14 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>GET /api/employees/[id] + /employees/[id] detail page: name/email/department/role/status all visible and resolved (not raw IDs). Manager field intentionally shows "Not tracked yet" rather than a fake value - the managerId/reporting-hierarchy schema field does not exist until Day 24, which is next.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="9">
       <c r="A24" s="11" t="n">
@@ -1586,10 +1598,14 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>PATCH /api/employees/[id] + inline edit form on the detail page (rename, reassign department/role, toggle active). Reassigning to a disabled department is rejected the same way creation is. 23 new unit/API tests + 3 new Playwright E2E tests across Days 20-23 (Partner creates+views+edits via the UI; Manager sees the list but not the create form; Preparer is fully blocked).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="9">
       <c r="A25" s="11" t="n">
@@ -8413,10 +8429,12 @@
       <c r="C19" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="11" t="n"/>
+      <c r="D19" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F19" s="11" t="n"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -439,7 +439,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:J168"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="8" min="1" max="2"/>
     <col width="28" customWidth="1" style="8" min="3" max="4"/>
@@ -1646,10 +1646,14 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>Migration adds self-referential managerId/manager/directReports on User (nullable - not every employee has a manager). employee.service.ts: assertManagerAssignable() rejects an unknown/cross-org manager, direct self-management (managerId === own id), and any longer cycle (walks up the proposed manager's own chain looking for the employee being updated). Wired into both createEmployee (optional managerId) and updateEmployee (managerId?: string | null - null clears it, omitted leaves it untouched). Employee detail page now shows the real manager (replacing Day 22's "Not tracked yet" placeholder) with a link to their profile, plus a manager select on both the create and edit forms. 6 new unit/service tests (assign, clear, unknown manager, self-management, 2-node cycle, 3-node cycle) + 3 new API route tests + 1 new Playwright E2E test (assign a manager, then verify a cycle attempt is rejected with the correct message).</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="9">
       <c r="A26" s="11" t="n">
@@ -7965,7 +7969,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:F103"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="8" min="1" max="1"/>
     <col width="34" customWidth="1" style="8" min="2" max="2"/>
@@ -8453,13 +8457,19 @@
       <c r="C20" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="11" t="n"/>
+      <c r="D20" s="11" t="n">
+        <v>24</v>
+      </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Self-referential manager relationship with cycle prevention (see Daily Plan Day 24).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="9">
       <c r="A21" s="11" t="inlineStr">
@@ -10302,7 +10312,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="8" min="1" max="1"/>
     <col width="12" customWidth="1" style="8" min="2" max="2"/>
@@ -11384,7 +11394,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="8" min="1" max="1"/>
     <col width="15" customWidth="1" style="8" min="2" max="2"/>
@@ -11590,7 +11600,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="8" min="1" max="1"/>
     <col width="110" customWidth="1" style="8" min="2" max="2"/>
@@ -11714,7 +11724,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="28" customWidth="1" style="8" min="1" max="1"/>
     <col width="20" customWidth="1" style="8" min="2" max="2"/>
@@ -11801,7 +11811,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:D39"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="48" customWidth="1" style="8" min="1" max="2"/>
     <col width="14" customWidth="1" style="8" min="3" max="3"/>
@@ -12681,7 +12691,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="8" min="1" max="1"/>
     <col width="58" customWidth="1" style="8" min="2" max="2"/>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J200"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="8" min="1" max="2"/>
@@ -1694,10 +1694,14 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>Skill model (org-scoped, unique name, isActive) + skill.service.ts CRUD, mirroring the Department pattern exactly (create/list/search/disable-enable). New /skills admin page (skill:view Manager+Partner, skill:manage Partner-only). Skill list shows an employee count per skill (informational, not an exception badge like the department one).</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="9">
       <c r="A27" s="11" t="n">
@@ -1738,10 +1742,14 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>EmployeeSkill join model (userId+skillId unique, level: BEGINNER/INTERMEDIATE/ADVANCED/EXPERT enum). Assignment lives on the employee detail page - assign/remove a skill with a level; re-assigning an already-held skill updates the level rather than erroring. Rejects an unknown or disabled skill. The PRD's AI-scored 'skills matrix' itself is Version 3 (Intelligent Allocation) - this is the baseline data entry only, per CLAUDE.md's build-incrementally principle.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="9">
       <c r="A28" s="11" t="n">
@@ -1782,10 +1790,14 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>Availability model (type: LEAVE/SICK/UNAVAILABLE, date range, optional reason), also on the employee detail page. 'Rules enforced' at this stage means the record itself has to be valid - end date &gt;= start date, and no overlapping periods for the same employee (service-layer check, not a Postgres exclusion constraint). No Task-aware blocking yet since Task doesn't exist - that's PRD Version 3's 'leave/availability consideration' in the allocation score, explicitly out of scope for this baseline day.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="9">
       <c r="A29" s="11" t="n">
@@ -7940,6 +7952,38 @@
         </is>
       </c>
     </row>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
   </sheetData>
   <autoFilter ref="A1:J161"/>
   <conditionalFormatting sqref="I2:I161">
@@ -7968,7 +8012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="8" min="1" max="1"/>
@@ -8485,13 +8529,19 @@
       <c r="C21" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="11" t="n"/>
+      <c r="D21" s="11" t="n">
+        <v>26</v>
+      </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Skill master + employee assignment with level (see Daily Plan Days 25-26).</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="9">
       <c r="A22" s="11" t="inlineStr">
@@ -8507,13 +8557,19 @@
       <c r="C22" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="11" t="n"/>
+      <c r="D22" s="11" t="n">
+        <v>27</v>
+      </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Leave/availability baseline model with date-validity + overlap enforcement (see Daily Plan Day 27).</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="9">
       <c r="A23" s="11" t="inlineStr">
@@ -10291,6 +10347,103 @@
         </is>
       </c>
     </row>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
   </sheetData>
   <autoFilter ref="A1:F100"/>
   <dataValidations count="1">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -1838,10 +1838,14 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>Client model (org-scoped, unique name, isActive) - deliberately just the top-level 'client/group' per PRD S6 (e.g. 'ABC Group'); legal entities/PAN/GSTIN/billing live on the Entity model in Day 32, contacts in Day 34, engagements in Day 35. client.service.ts createClient() rejects an exact duplicate name in the org (409 CONFLICT), same pattern as Department. Gated on the pre-existing client:editStructural permission (creating a client is a structural action) - no new permission needed, the catalog already had the client:view/viewAll/editContact/editStructural split from Day 14.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="9">
       <c r="A30" s="11" t="n">
@@ -1882,10 +1886,14 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>listClients() with real pagination (page/pageSize, default 20/page) - unlike Department/Employee's unpaginated lists, since a firm's client roster can run into the hundreds. Also search (case-insensitive name contains) and includeInactive. Splits on client:viewAll vs plain client:view: viewAll (Manager+Partner) sees the real paginated list, view-only (Preparer) gets an empty page rather than firm-wide access, since there's no Task table yet to compute 'assigned to me' against - see RBAC.md's updated known-gaps note. /clients page + Previous/Next pager in the UI.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="9">
       <c r="A31" s="11" t="n">
@@ -1926,10 +1934,14 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>Client detail page (/clients/[id]): name, status, created date. Placeholder section noting entities/contacts/engagements land in later days, matching the same 'coming soon' pattern used elsewhere for not-yet-built features. GET /api/clients/[id] applies the same viewAll-vs-assigned scoping as the list (a Preparer gets 404, not the record) - this was a real gap I found and fixed while building the route (the single-GET endpoint hadn't inherited the list's scoping check).</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="9">
       <c r="A32" s="11" t="n">
@@ -1970,10 +1982,14 @@
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>PATCH /api/clients/[id] (rename + isActive toggle) + edit form on the detail page, mirroring Department's edit pattern exactly. 'Inactive-client rules enforced' scoped to what's checkable today: an inactive client drops out of the default list (same as Department's isActive filter) - richer enforcement (e.g. blocking a new engagement against an inactive client) waits for Engagement to exist (Day 35).</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="9">
       <c r="A33" s="11" t="n">
@@ -8585,13 +8601,19 @@
       <c r="C23" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="11" t="n"/>
+      <c r="D23" s="11" t="n">
+        <v>31</v>
+      </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Client/group master (name + status) with pagination, search, viewAll/assigned scoping, and lifecycle edit (see Daily Plan Days 28-31). Entities/Contacts/Engagements are separate later rows.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="9">
       <c r="A24" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2030,10 +2030,14 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>ClientEntity model (PRD S6's legal entity under a client/group, e.g. 'ABC Private Limited' under 'ABC Group') - name, PAN/GSTIN/CIN (format-validated, normalised uppercase), account manager (Employee FK), phone/email, isActive. Primary Contact (Contact model, Day 34) and Services/Billing/Engagement Start (Engagement model, Day 35) are the same PRD table's remaining fields, deliberately still deferred - those need tables that don't exist yet. Name unique per client (not per org - two different client groups can each have an entity called the same thing); PAN and GSTIN unique per org (they're real national tax-identity numbers, a duplicate is a genuine data error). Gated on the existing client:editStructural permission. Entity creation lives inline on the client detail page.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="9">
       <c r="A34" s="11" t="n">
@@ -2074,10 +2078,14 @@
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Entity list (inline table on the client detail page, name/PAN/GSTIN/account manager/status) + a dedicated entity detail page (all fields, edit form) at /clients/[id]/entities/[entityId]. GET routes apply the same client:viewAll-vs-assigned scoping already established for Client itself (a Preparer gets 404, not the record) - this was carried through consistently rather than re-derived. Also: found and fixed a test bug while verifying this (capturing a URL before waiting for navigation to complete), and confirmed a one-off Supabase network blip during the first E2E run wasn't a real regression by re-running clean.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="9">
       <c r="A35" s="11" t="n">
@@ -8629,13 +8637,19 @@
       <c r="C24" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="11" t="n"/>
+      <c r="D24" s="11" t="n">
+        <v>33</v>
+      </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Legal entity master under a client/group (PAN/GSTIN/CIN/account manager) with list + detail (see Daily Plan Days 32-33). Contacts/Engagements are separate later rows.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="9">
       <c r="A25" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2126,10 +2126,14 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Contact model (PRD S6/S38's 'Contact | Client contact', referenced as an entity's 'Primary Contact') - name, designation, phone, email, isPrimary. Belongs to a ClientEntity (not the top-level Client), matching where the PRD's own field table places 'Primary Contact'. Unlike entity/client-level fields, gated on client:editContact (Manager+Partner) rather than client:editStructural (Partner-only) - RBAC.md's own description names 'contact notes' as exactly this permission's use case, so no new permission or grant changes were needed. 'Duplicate handling' = exact name uniqueness per entity (same pattern as every other master this session). At most one primary contact per entity, enforced transactionally in the service layer (setting one clears any existing primary) rather than as a hard uniqueness conflict the caller has to resolve first. No isActive lifecycle like the other masters - a contact who's left is just removed (hard delete), the lowest-stakes record in this whole domain. Found and fixed a real staleness bug while testing: the entity's own 'Primary contact' field is computed server-side and was going stale after adding/changing a contact client-side, since only the Contacts table's own local state was refreshed - fixed by also calling router.refresh() (same category of bug as the Day 24 manager-dropdown staleness issue).</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="9">
       <c r="A36" s="11" t="n">
@@ -8665,13 +8669,19 @@
       <c r="C25" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="11" t="n"/>
+      <c r="D25" s="11" t="n">
+        <v>34</v>
+      </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Client contact master under a legal entity, with primary-contact exclusivity (see Daily Plan Day 34).</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="9">
       <c r="A26" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2174,10 +2174,14 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="n"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>BLOCKED: this row's own acceptance check is 'Service linked to entity/client', but Service doesn't exist yet - Service Master is Days 37-41, later in the same Daily Plan. An Engagement literally cannot be built to spec without something to link to. Per CLAUDE.md: 'don't silently carry it forward or weaken the test to make it pass' - flagging this rather than either skipping silently or building a fake/placeholder service link. Plan: build Service Master (Days 37-41) next, then come straight back to complete this row against the real Service model.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="9">
       <c r="A37" s="11" t="n">
@@ -2218,10 +2222,14 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Client.instructions (free-text, PRD S6's 'client-specific instructions') - persistent, editable notes on the client/group. Gated on client:editContact (Manager+Partner), not client:editStructural, matching how Contacts (Day 34) were classified - lightweight day-to-day content gets its own PATCH route (/api/clients/[id]/instructions) separate from the name/isActive one, same reasoning as Contacts being a separate resource from the entity's own fields. Deliberately did not build a separate 'responsible employee(s)' assignment system - ClientEntity.accountManagerId (Day 32) already covers that at the entity level, and the PRD gives no detail suggesting a distinct client-level responsibility concept is needed yet.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="9">
       <c r="A38" s="11" t="n">
@@ -8700,10 +8708,14 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="n"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Needs Service Master (Days 37-41) to exist first - see Daily Plan Day 35.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="9">
       <c r="A27" s="11" t="inlineStr">
@@ -8719,13 +8731,19 @@
       <c r="C27" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="11" t="n"/>
+      <c r="D27" s="11" t="n">
+        <v>36</v>
+      </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Persistent client instructions field (see Daily Plan Day 36).</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="9">
       <c r="A28" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J200"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="8" min="1" max="2"/>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>BLOCKED: this row's own acceptance check is 'Service linked to entity/client', but Service doesn't exist yet - Service Master is Days 37-41, later in the same Daily Plan. An Engagement literally cannot be built to spec without something to link to. Per CLAUDE.md: 'don't silently carry it forward or weaken the test to make it pass' - flagging this rather than either skipping silently or building a fake/placeholder service link. Plan: build Service Master (Days 37-41) next, then come straight back to complete this row against the real Service model.</t>
+          <t>Unblocked: Service Master (Days 37-41) is now built. Ready to build the Engagement model linking a ClientEntity to a Service, per this row's acceptance check.</t>
         </is>
       </c>
     </row>
@@ -2270,10 +2270,14 @@
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>Service model created (name, org-scoped), createService with required-metadata validation and duplicate-name-per-parent rejection. API: POST/GET /api/services. Unit/API tests cover happy path, validation error, permission (403 Preparer), and auth (401 logged out).</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="9">
       <c r="A39" s="11" t="n">
@@ -2314,10 +2318,14 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Self-referential Service.parentId with cycle prevention (assertParentValid walks up from proposed parent) mirroring the Day 24 manager-hierarchy pattern. listServiceTree returns a nested children[] tree; UI renders it indented and recursively. Tests cover nesting, self-parent rejection, and circular-parent rejection.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="9">
       <c r="A40" s="11" t="n">
@@ -2358,10 +2366,14 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>updateService supports isActive toggle (Disable/Enable in UI); assertServiceAssignable throws SERVICE_DISABLED for a disabled service, ready for Engagement (Day 35) to consume. Tests cover disable, the assignability check failing while disabled, and re-enabling.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="9">
       <c r="A41" s="11" t="n">
@@ -2402,10 +2414,14 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>Service.departmentId (FK to Department, validated) and Service.expectedSkillLevel (SkillLevel enum) stored and returned via getService/listServiceTree/updateService; set and edited from the Service create form and detail-page edit form. Covered by the Day 37 create test (department + skill level asserted on the created record) and the Day 39 update tests.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="9">
       <c r="A42" s="11" t="n">
@@ -2446,10 +2462,14 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>ChecklistTemplate (1:1 with Service, @@unique serviceId) + ChecklistItem models; checklist.service.ts creates a template with its starting items in one call, and supports add/remove items. API: GET/POST /api/services/[id]/checklist, POST items, DELETE items/[itemId]. UI: ServiceChecklist.tsx on the service detail page. Tests cover empty state, template creation, rejecting a second template (409), rejecting an empty item list, adding/removing items, and a 404 when adding an item before any template exists.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="9">
       <c r="A43" s="11" t="n">
@@ -7988,38 +8008,6 @@
         </is>
       </c>
     </row>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
   </sheetData>
   <autoFilter ref="A1:J161"/>
   <conditionalFormatting sqref="I2:I161">
@@ -8048,7 +8036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="30" customWidth="1" style="8" min="1" max="1"/>
@@ -8708,12 +8696,12 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Needs Service Master (Days 37-41) to exist first - see Daily Plan Day 35.</t>
+          <t>Unblocked now that Service Master exists (Daily Plan Days 37-41) - ready to build against the real Service model (see Daily Plan Day 35).</t>
         </is>
       </c>
     </row>
@@ -8759,13 +8747,19 @@
       <c r="C28" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="11" t="n"/>
+      <c r="D28" s="11" t="n">
+        <v>39</v>
+      </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Service model with required metadata, parent-child hierarchy (cycle-safe), and edit/disable lifecycle (see Daily Plan Days 37-39).</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="9">
       <c r="A29" s="11" t="inlineStr">
@@ -8781,13 +8775,19 @@
       <c r="C29" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="11" t="n"/>
+      <c r="D29" s="11" t="n">
+        <v>41</v>
+      </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Department + expected skill level requirements, and a reusable checklist template attached per service, are done (Daily Plan Days 40-41). TAT/effort/reviewer defaults (Day 42) not yet built.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="9">
       <c r="A30" s="11" t="inlineStr">
@@ -10411,103 +10411,6 @@
         </is>
       </c>
     </row>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
   </sheetData>
   <autoFilter ref="A1:F100"/>
   <dataValidations count="1">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2174,12 +2174,12 @@
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>Unblocked: Service Master (Days 37-41) is now built. Ready to build the Engagement model linking a ClientEntity to a Service, per this row's acceptance check.</t>
+          <t>Engagement model links a ClientEntity to a Service (PRD S6: Services/Engagement Start/Billing Structure/Status per entity), with engagementStart, billingStructure (Monthly/Assignment), and isActive (terminate/reactivate). Blocks engaging a disabled service (reuses Day 39 assertServiceAssignable) and re-disabling mid-engagement on reactivation. Gated on client:editStructural (its own permission description already named "terminate an engagement"). Nested under /clients/[id]/entities/[entityId]/engagements; added assertEntityBelongsToClient guard to entity.service.ts so the nested API routes reject an entityId that does not belong to the client id in the URL (closes a latent gap the sibling Contact routes still have - flagged separately, not fixed here). Unit/API + Playwright E2E tests cover happy path, disabled-service rejection, duplicate engagement (409), cross-client entity mismatch (404), permission (403 Manager), and auth (401 logged out).</t>
         </is>
       </c>
     </row>
@@ -8693,15 +8693,17 @@
       <c r="C26" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="11" t="n"/>
+      <c r="D26" s="11" t="n">
+        <v>35</v>
+      </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>Unblocked now that Service Master exists (Daily Plan Days 37-41) - ready to build against the real Service model (see Daily Plan Day 35).</t>
+          <t>Client-service engagement linking a ClientEntity to a Service, with billing structure and terminate/reactivate lifecycle (see Daily Plan Day 35).</t>
         </is>
       </c>
     </row>

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2510,10 +2510,14 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>TAT/effort/reviewer defaults (turnaroundDays, estimatedEffortMinHours/MaxHours, reviewRequired) were already stored via the Day 37-41 Service model, but the create/edit UI forms did not expose the effort range or standardDocuments fields (API-only). Closed that gap: both fields now on ServicesAdmin.tsx (create) and ServiceDetail.tsx (edit), plus a new cross-field rule (estimatedEffortMaxHours must be &gt;= estimatedEffortMinHours, checked on both create and partial update) since an inverted range is invalid data, not a valid one. Unit/API + E2E tests cover the full round trip and the rejection.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="9">
       <c r="A44" s="11" t="n">
@@ -2554,10 +2558,14 @@
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>New RecurringConfig model (1:1 with a recurring Service): frequency (Monthly/Quarterly/Annually, PRD S32) + dayOfMonth (capped 1-28) + monthOfYear (Annually only). computeNextOccurrence is a pure, unit-tested function - "generate a test recurring instance" is literally calling it, since actually generating a Task from it is Task Engine's job (Day 44+), same pattern as Day 41's checklist template being just the template. API + UI (service detail page, shown only when isRecurring) let a Partner set the calendar and preview the next occurrence. Gated on service:manage to configure, service:view to see it.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="9">
       <c r="A45" s="11" t="n">
@@ -8778,16 +8786,16 @@
         <v>3</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>Department + expected skill level requirements, and a reusable checklist template attached per service, are done (Daily Plan Days 40-41). TAT/effort/reviewer defaults (Day 42) not yet built.</t>
+          <t>Department + skill requirements, standard checklist, and TAT/effort/reviewer defaults - all on the Service model (see Daily Plan Days 40-42).</t>
         </is>
       </c>
     </row>
@@ -8805,13 +8813,19 @@
       <c r="C30" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="11" t="n"/>
+      <c r="D30" s="11" t="n">
+        <v>43</v>
+      </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Recurrence calendar (frequency + day/month) per recurring service, with a next-occurrence computation baseline for Task Engine to consume later (see Daily Plan Day 43).</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="9">
       <c r="A31" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2606,10 +2606,14 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>Task model (PRD S11 core fields, minus the ones the roadmap gives their own later day - assignedTo/reviewer is Assignment, startDate/dueDate is Dates, attachments/dependencies/checklist/subtasks/comments are their own tables/days). Status uses the full PRD S12 vocabulary as a fixed enum (declared now since it is already-specified vocabulary), defaulting every task to NEW - the actual transition state machine is this phase's own "Workflow" day, not built yet. Client/entity/service validation (this row's own acceptance check) is real: confirms the entity belongs to the client, that an ACTIVE Engagement exists linking the entity to the service, and that the service itself has not since been disabled (an engagement can stay active after its service is disabled - no automatic cascades). Task ID generation (Day 45) implemented together with creation since every task needs one immediately: TASK-&lt;year&gt;-&lt;month&gt;-&lt;sequence&gt;, atomically incremented per org per month. ASSUMPTION flagged for founder review: the PRD's own example id format (GST-ABC-2026-09-00127) abbreviates service/client names, but neither model has a short-code field to derive that from - used a simpler unique/readable format instead of guessing at one; revisit if a specific format is wanted. Unit/API + E2E tests cover the happy path, all three validation failures (entity/client mismatch, no engagement, disabled service), permission (403), and auth (401).</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="9">
       <c r="A46" s="11" t="n">
@@ -2650,10 +2654,14 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>Task model (PRD S11 core fields, minus the ones the roadmap gives their own later day - assignedTo/reviewer is Assignment, startDate/dueDate is Dates, attachments/dependencies/checklist/subtasks/comments are their own tables/days). Status uses the full PRD S12 vocabulary as a fixed enum (declared now since it is already-specified vocabulary), defaulting every task to NEW - the actual transition state machine is this phase's own "Workflow" day, not built yet. Client/entity/service validation (this row's own acceptance check) is real: confirms the entity belongs to the client, that an ACTIVE Engagement exists linking the entity to the service, and that the service itself has not since been disabled (an engagement can stay active after its service is disabled - no automatic cascades). Task ID generation (Day 45) implemented together with creation since every task needs one immediately: TASK-&lt;year&gt;-&lt;month&gt;-&lt;sequence&gt;, atomically incremented per org per month. ASSUMPTION flagged for founder review: the PRD's own example id format (GST-ABC-2026-09-00127) abbreviates service/client names, but neither model has a short-code field to derive that from - used a simpler unique/readable format instead of guessing at one; revisit if a specific format is wanted. Unit/API + E2E tests cover the happy path, all three validation failures (entity/client mismatch, no engagement, disabled service), permission (403), and auth (401).</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="9">
       <c r="A47" s="11" t="n">
@@ -8841,13 +8849,19 @@
       <c r="C31" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="11" t="n"/>
+      <c r="D31" s="11" t="n">
+        <v>45</v>
+      </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Manual task creation with real client/entity/service (active engagement) validation, and atomic per-org-per-month task ID generation (see Daily Plan Days 44-45).</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="9">
       <c r="A32" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2702,10 +2702,14 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J47" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>Filters implemented for status, client, and priority (query params, validated). PARTIALLY DONE by design: this row also lists an assignee filter and a date filter, but neither has a backing field yet (assignedToId is Assignment/Day 49, dueDate is Dates/Day 51) - both will be added to this same GET /api/tasks route + filter bar once those days land, not guessed at now. Same task:viewAll/assigned scoping as task list itself (empty for a Preparer today, same known gap as Client). Unit/API + E2E tests cover each filter and an invalid filter value.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="9">
       <c r="A48" s="11" t="n">
@@ -8877,13 +8881,19 @@
       <c r="C32" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="11" t="n"/>
+      <c r="D32" s="11" t="n">
+        <v>46</v>
+      </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Task queue with status/client/priority filters; assignee/date filters follow once Assignment (Day 49) and Dates (Day 51) add their fields (see Daily Plan Day 46).</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="9">
       <c r="A33" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2750,10 +2750,14 @@
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>Task detail page at /tasks/[id]: Core (Task Number, Title, Client, Entity, Department, Service, Priority, Status, Source, Created) plus related data that already exists - the Engagement for this entity/service pairing (billing structure, engagement start, active/terminated), fetched separately from the task row to demonstrate real related-data loading, not just denormalized fields. Scoped to task:viewAll like the list (same known gap). PRD S18 describes a much larger screen (Client Instruction, AI Interpretation, Checklist, Attachments, Working Papers, Time, Comments, Client Communication, Review, Activity Timeline) - almost none of which exists yet (AI intake, attachments, time tracking, comments, review, and activity timeline are all separate later days/phases); this page adds each section as its own day builds it, rather than stubbing placeholders now. Also added GET /api/tasks/[id] (same route pattern as Client/Entity/Service) as the natural attachment point for status/assignment mutations once those days land. Unit/API + E2E tests cover the happy path, not-found, permission scoping, and auth.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="82.05" customHeight="1" s="9">
       <c r="A49" s="11" t="n">
@@ -8909,13 +8913,19 @@
       <c r="C33" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="11" t="n"/>
+      <c r="D33" s="11" t="n">
+        <v>47</v>
+      </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Task workspace with core fields and related Engagement data; grows section by section as later days (checklist, comments, attachments, etc.) land (see Daily Plan Day 47).</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="9">
       <c r="A34" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2798,10 +2798,14 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>Full PRD S12 status graph implemented as a fixed adjacency list, tested exhaustively - one test checks all 15x15=225 status-pair combinations against an independently-listed edge set (not imported from the implementation, so the test actually verifies against the spec). Two judgment calls the PRD diagram leaves undrawn, documented in code: CORRECTION_REQUIRED loops back to IN_PROGRESS (rework has to re-enter the work loop somewhere); CANCELLED is reachable from any non-terminal status (matches task:cancel permission wording with no qualifier). Every transition is logged to a new TaskStatusHistory table - succeeded AND rejected attempts both - satisfying this row's own "blocked and logged" requirement and PRD S12's "complete timestamp trail"; Task Engine's own later "History" day reads from this same table rather than duplicating it. Permission-gated by target status: task:review for the reviewer decisions (REVIEW_IN_PROGRESS/APPROVED/CORRECTION_REQUIRED), task:cancel for CANCELLED, task:updateStatus for everything else - matches the existing permission descriptions exactly, no new permissions needed. UI on the task detail page only offers buttons for transitions both graph-valid AND permitted. Unit tests cover the full matrix + permission mapping; API tests walk the complete happy path plus the two branch/loop cases, confirm rejection+logging, and cover every permission boundary; E2E walks the UI through several real transitions.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="9">
       <c r="A50" s="11" t="n">
@@ -8941,13 +8945,19 @@
       <c r="C34" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="11" t="n"/>
+      <c r="D34" s="11" t="n">
+        <v>48</v>
+      </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F34" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Full PRD S12 status state machine, exhaustively tested, every transition (valid and blocked) logged to TaskStatusHistory (see Daily Plan Day 48).</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="9">
       <c r="A35" s="11" t="inlineStr">

--- a/docs/roadmap.xlsx
+++ b/docs/roadmap.xlsx
@@ -2846,10 +2846,14 @@
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J50" s="11" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>Task.assignedToId added. Eligibility is a deliberately small MVP proxy - active + same department as the task (the first and most basic factor PRD S13 itself lists) - not the full Allocation Engine (skill/authority/client-restrictions/experience/capacity/deadlines/complexity/proficiency/availability/continuity), which is its own much later phase needing infrastructure (capacity model, scoring) this day does not build. The eligible-employees endpoint pre-filters the selectable set itself, not just validates after selection. Assigning requires AWAITING_ALLOCATION and no existing assignee, and atomically transitions the task to ASSIGNED via the same TaskStatusHistory logging as Day 48. Also closed the "no assignment mechanism yet" gap flagged since Day 44/46/47/48: task:view (without viewAll) now genuinely resolves to "tasks assigned to me" in both the list and detail routes/pages, and the list gained the promised assignee filter. docs/RBAC.md updated. Found and fixed a real bug along the way: TaskStatusControl kept local status state that never resynced when a sibling (TaskAssignment) changed the task's status via its own router.refresh() - same staleness pattern as the Day 24/34 sibling-state bugs.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="9">
       <c r="A51" s="11" t="n">
@@ -8973,13 +8977,19 @@
       <c r="C35" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="11" t="n"/>
+      <c r="D35" s="11" t="n">
+        <v>49</v>
+      </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="F35" s="11" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>First-time assignment with eligible/active filtering (see Daily Plan Day 49). Reassignment (Day 50, with its own history requirement) not yet built.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="9">
       <c r="A36" s="11" t="inlineStr">
